--- a/rules/CORE-000158/negative/01/data/unit-test-coreid-CG0163-negative.xlsx
+++ b/rules/CORE-000158/negative/01/data/unit-test-coreid-CG0163-negative.xlsx
@@ -53,11 +53,11 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <i/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <i/>
     </font>
     <font>
       <sz val="11"/>
@@ -112,8 +112,8 @@
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
@@ -457,10 +457,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="4" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -484,10 +484,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="4" t="str">
         <v>co.xpt</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>Comments</v>
       </c>
     </row>
@@ -523,23 +523,20 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>co.xpt</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="4" t="str">
         <v>Record</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="4">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="str">
-        <v>RDOMAIN</v>
-      </c>
-      <c r="F2" s="2" t="str">
-        <v>PE</v>
+      <c r="E2" s="4" t="str">
+        <v>IDVAR</v>
       </c>
     </row>
     <row r="3">
@@ -556,7 +553,10 @@
         <v>6</v>
       </c>
       <c r="E3" s="2" t="str">
-        <v>IDVAR</v>
+        <v>RDOMAIN</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <v>PE</v>
       </c>
     </row>
   </sheetData>
@@ -618,502 +618,502 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="str">
+      <c r="A2" s="5" t="str">
         <v>Study Identifier</v>
       </c>
-      <c r="B2" s="4" t="str">
+      <c r="B2" s="5" t="str">
         <v>Domain Abbreviation</v>
       </c>
-      <c r="C2" s="4" t="str">
+      <c r="C2" s="5" t="str">
         <v>Related Domain Abbreviation</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="5" t="str">
         <v>Unique Subject Identifier</v>
       </c>
-      <c r="E2" s="4" t="str">
+      <c r="E2" s="5" t="str">
         <v>Sequence Number</v>
       </c>
-      <c r="F2" s="4" t="str">
+      <c r="F2" s="5" t="str">
         <v>Identifying Variable</v>
       </c>
-      <c r="G2" s="4" t="str">
+      <c r="G2" s="5" t="str">
         <v>Identifying Variable Value</v>
       </c>
-      <c r="H2" s="4" t="str">
+      <c r="H2" s="5" t="str">
         <v>Comment Reference</v>
       </c>
-      <c r="I2" s="4" t="str">
+      <c r="I2" s="5" t="str">
         <v>Comment</v>
       </c>
-      <c r="J2" s="4" t="str">
+      <c r="J2" s="5" t="str">
         <v>Comment</v>
       </c>
-      <c r="K2" s="4" t="str">
+      <c r="K2" s="5" t="str">
         <v>Comment</v>
       </c>
-      <c r="L2" s="4" t="str">
+      <c r="L2" s="5" t="str">
         <v>Evaluator</v>
       </c>
-      <c r="M2" s="4" t="str">
+      <c r="M2" s="5" t="str">
         <v>Visitnumber</v>
       </c>
-      <c r="N2" s="4" t="str">
+      <c r="N2" s="5" t="str">
         <v>Date/Time of Comment</v>
       </c>
-      <c r="O2" s="4" t="str">
+      <c r="O2" s="5" t="str">
         <v>Study Day of Comment</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="str">
+      <c r="A3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="B3" s="4" t="str">
+      <c r="B3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="C3" s="4" t="str">
+      <c r="C3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="D3" s="4" t="str">
+      <c r="D3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="E3" s="4" t="str">
+      <c r="E3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="F3" s="4" t="str">
+      <c r="F3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="G3" s="4" t="str">
+      <c r="G3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="H3" s="4" t="str">
+      <c r="H3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="I3" s="4" t="str">
+      <c r="I3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="J3" s="4" t="str">
+      <c r="J3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="K3" s="4" t="str">
+      <c r="K3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="L3" s="4" t="str">
+      <c r="L3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="M3" s="4" t="str">
+      <c r="M3" s="5" t="str">
         <v>Num</v>
       </c>
-      <c r="N3" s="4" t="str">
+      <c r="N3" s="5" t="str">
         <v>Char</v>
       </c>
-      <c r="O3" s="4" t="str">
+      <c r="O3" s="5" t="str">
         <v>Num</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4">
+      <c r="A4" s="5">
         <v>50</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
         <v>50</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>50</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>50</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>8</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="5">
         <v>50</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>50</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="5">
         <v>50</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="5">
         <v>50</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>50</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="5">
         <v>50</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="5">
         <v>50</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="5">
         <v>8</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="5">
         <v>50</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="5">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>1234</v>
       </c>
-      <c r="B5" s="5" t="str">
+      <c r="B5" s="4" t="str">
         <v>CO</v>
       </c>
-      <c r="C5" s="5" t="str">
-        <v/>
-      </c>
-      <c r="D5" s="5" t="str">
+      <c r="C5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="D5" s="4" t="str">
         <v>AB-99</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>1</v>
       </c>
-      <c r="F5" s="5" t="str">
-        <v/>
-      </c>
-      <c r="G5" s="5" t="str">
-        <v/>
-      </c>
-      <c r="H5" s="5" t="str">
-        <v/>
-      </c>
-      <c r="I5" s="5" t="str">
+      <c r="F5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="G5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="H5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="str">
         <v xml:space="preserve">Patient was then transferred to tertiary care centre since his condition continued to deteriorate </v>
       </c>
-      <c r="J5" s="5" t="str">
-        <v/>
-      </c>
-      <c r="K5" s="5" t="str">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="str">
+      <c r="J5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="K5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L5" s="4" t="str">
         <v>PRINCIPAL INVESTIGATOR</v>
       </c>
-      <c r="M5" s="5" t="str">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="str">
+      <c r="M5" s="4" t="str">
+        <v/>
+      </c>
+      <c r="N5" s="4" t="str">
         <v>2019-11-08</v>
       </c>
-      <c r="O5" s="5" t="str">
+      <c r="O5" s="4" t="str">
         <v>134</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>1234</v>
       </c>
-      <c r="B6" s="5" t="str">
+      <c r="B6" s="4" t="str">
         <v>CO</v>
       </c>
       <c r="C6" s="6" t="str">
         <v>PE</v>
       </c>
-      <c r="D6" s="5" t="str">
+      <c r="D6" s="4" t="str">
         <v>XX-11</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>2</v>
       </c>
       <c r="F6" s="6" t="str">
         <v/>
       </c>
-      <c r="G6" s="5" t="str">
-        <v/>
-      </c>
-      <c r="H6" s="5" t="str">
+      <c r="G6" s="4" t="str">
+        <v/>
+      </c>
+      <c r="H6" s="4" t="str">
         <v>VISIT 7</v>
       </c>
-      <c r="I6" s="5" t="str">
+      <c r="I6" s="4" t="str">
         <v>Visit was delayed by a day due to strike at hospital</v>
       </c>
-      <c r="J6" s="5" t="str">
-        <v/>
-      </c>
-      <c r="K6" s="5" t="str">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="str">
+      <c r="J6" s="4" t="str">
+        <v/>
+      </c>
+      <c r="K6" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L6" s="4" t="str">
         <v>PRINCIPAL INVESTIGATOR</v>
       </c>
-      <c r="M6" s="5" t="str">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="str">
+      <c r="M6" s="4" t="str">
+        <v/>
+      </c>
+      <c r="N6" s="4" t="str">
         <v>2020-01-14</v>
       </c>
-      <c r="O6" s="5" t="str">
+      <c r="O6" s="4" t="str">
         <v>201</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>1234</v>
       </c>
-      <c r="B7" s="5" t="str">
+      <c r="B7" s="4" t="str">
         <v>CO</v>
       </c>
-      <c r="C7" s="5" t="str">
-        <v/>
-      </c>
-      <c r="D7" s="5" t="str">
+      <c r="C7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="D7" s="4" t="str">
         <v>YY-20</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>3</v>
       </c>
-      <c r="F7" s="5" t="str">
+      <c r="F7" s="4" t="str">
         <v>AESEQ</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>7</v>
       </c>
-      <c r="H7" s="5" t="str">
+      <c r="H7" s="4" t="str">
         <v>PAGE 650</v>
       </c>
-      <c r="I7" s="5" t="str">
+      <c r="I7" s="4" t="str">
         <v xml:space="preserve">On 01JAN2020 the woman and her son were bitten by a stray dog while walking nearby to their house. The woman sustained bites on her thigh while her son had bites on his left foot. Dog was killed and </v>
       </c>
-      <c r="J7" s="5" t="str">
+      <c r="J7" s="4" t="str">
         <v>buried without laboratory investigation for rabies. Women washed the wounds of her child shortly after the incident and then took him to the healthcare unit where he received a rabies vaccine and</v>
       </c>
-      <c r="K7" s="5" t="str">
+      <c r="K7" s="4" t="str">
         <v>completed a full course of standard vaccines.</v>
       </c>
-      <c r="L7" s="5" t="str">
+      <c r="L7" s="4" t="str">
         <v>PRINCIPAL INVESTIGATOR</v>
       </c>
-      <c r="M7" s="5" t="str">
-        <v/>
-      </c>
-      <c r="N7" s="5" t="str">
+      <c r="M7" s="4" t="str">
+        <v/>
+      </c>
+      <c r="N7" s="4" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>1234</v>
       </c>
-      <c r="B8" s="5" t="str">
+      <c r="B8" s="4" t="str">
         <v>CO</v>
       </c>
-      <c r="C8" s="5" t="str">
+      <c r="C8" s="4" t="str">
         <v>EX</v>
       </c>
-      <c r="D8" s="5" t="str">
+      <c r="D8" s="4" t="str">
         <v>ZZ-23</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>4</v>
       </c>
-      <c r="F8" s="5" t="str">
+      <c r="F8" s="4" t="str">
         <v>EXGRPID</v>
       </c>
-      <c r="G8" s="5" t="str">
+      <c r="G8" s="4" t="str">
         <v>COMBO1</v>
       </c>
-      <c r="H8" s="5" t="str">
+      <c r="H8" s="4" t="str">
         <v>PAGE 320-355</v>
       </c>
-      <c r="I8" s="5" t="str">
+      <c r="I8" s="4" t="str">
         <v>Medicine was administered under supervision of Sub investigator as PI was on leave</v>
       </c>
-      <c r="J8" s="5" t="str">
-        <v/>
-      </c>
-      <c r="K8" s="5" t="str">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="str">
+      <c r="J8" s="4" t="str">
+        <v/>
+      </c>
+      <c r="K8" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L8" s="4" t="str">
         <v>PRINCIPAL INVESTIGATOR</v>
       </c>
-      <c r="M8" s="5" t="str">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="str">
+      <c r="M8" s="4" t="str">
+        <v/>
+      </c>
+      <c r="N8" s="4" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>1234</v>
       </c>
-      <c r="B9" s="5" t="str">
+      <c r="B9" s="4" t="str">
         <v>CO</v>
       </c>
-      <c r="C9" s="5" t="str">
-        <v/>
-      </c>
-      <c r="D9" s="5" t="str">
+      <c r="C9" s="4" t="str">
+        <v/>
+      </c>
+      <c r="D9" s="4" t="str">
         <v>AB-99</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>5</v>
       </c>
-      <c r="F9" s="5" t="str">
+      <c r="F9" s="4" t="str">
         <v>VSGRPID</v>
       </c>
-      <c r="G9" s="5" t="str">
+      <c r="G9" s="4" t="str">
         <v>VS2</v>
       </c>
-      <c r="H9" s="5" t="str">
-        <v/>
-      </c>
-      <c r="I9" s="5" t="str">
+      <c r="H9" s="4" t="str">
+        <v/>
+      </c>
+      <c r="I9" s="4" t="str">
         <v>Vital signs were recorded by casualty physician</v>
       </c>
-      <c r="J9" s="5" t="str">
-        <v/>
-      </c>
-      <c r="K9" s="5" t="str">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="str">
+      <c r="J9" s="4" t="str">
+        <v/>
+      </c>
+      <c r="K9" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L9" s="4" t="str">
         <v>PRINCIPAL INVESTIGATOR</v>
       </c>
-      <c r="M9" s="5" t="str">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="str">
+      <c r="M9" s="4" t="str">
+        <v/>
+      </c>
+      <c r="N9" s="4" t="str">
         <v/>
       </c>
     </row>
     <row r="10" xml:space="preserve">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>1234</v>
       </c>
-      <c r="B10" s="5" t="str">
+      <c r="B10" s="4" t="str">
         <v>CO</v>
       </c>
-      <c r="C10" s="5" t="str">
+      <c r="C10" s="4" t="str">
         <v>DM</v>
       </c>
-      <c r="D10" s="5" t="str">
+      <c r="D10" s="4" t="str">
         <v>XX-11</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>6</v>
       </c>
-      <c r="F10" s="5" t="str" xml:space="preserve">
+      <c r="F10" s="4" t="str" xml:space="preserve">
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>4</v>
       </c>
-      <c r="H10" s="5" t="str">
-        <v/>
-      </c>
-      <c r="I10" s="5" t="str">
+      <c r="H10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="I10" s="4" t="str">
         <v>Visit was delayed by a day due to hospital holiday</v>
       </c>
-      <c r="J10" s="5" t="str">
-        <v/>
-      </c>
-      <c r="K10" s="5" t="str">
-        <v/>
-      </c>
-      <c r="L10" s="5" t="str">
+      <c r="J10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="K10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L10" s="4" t="str">
         <v>PRINCIPAL INVESTIGATOR</v>
       </c>
-      <c r="M10" s="5" t="str">
-        <v/>
-      </c>
-      <c r="N10" s="5" t="str">
+      <c r="M10" s="4" t="str">
+        <v/>
+      </c>
+      <c r="N10" s="4" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <v>1234</v>
       </c>
-      <c r="B11" s="5" t="str">
+      <c r="B11" s="4" t="str">
         <v>CO</v>
       </c>
-      <c r="C11" s="5" t="str">
-        <v/>
-      </c>
-      <c r="D11" s="5" t="str">
+      <c r="C11" s="4" t="str">
+        <v/>
+      </c>
+      <c r="D11" s="4" t="str">
         <v>YY-20</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>7</v>
       </c>
-      <c r="F11" s="5" t="str">
-        <v/>
-      </c>
-      <c r="G11" s="5" t="str">
-        <v/>
-      </c>
-      <c r="H11" s="5" t="str">
+      <c r="F11" s="4" t="str">
+        <v/>
+      </c>
+      <c r="G11" s="4" t="str">
+        <v/>
+      </c>
+      <c r="H11" s="4" t="str">
         <v>VISIT 4</v>
       </c>
-      <c r="I11" s="5" t="str">
+      <c r="I11" s="4" t="str">
         <v>Visit was delayed by a day due to hospital holiday</v>
       </c>
-      <c r="J11" s="5" t="str">
-        <v/>
-      </c>
-      <c r="K11" s="5" t="str">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="str">
+      <c r="J11" s="4" t="str">
+        <v/>
+      </c>
+      <c r="K11" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L11" s="4" t="str">
         <v>PRINCIPAL INVESTIGATOR</v>
       </c>
-      <c r="M11" s="5" t="str">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="str">
+      <c r="M11" s="4" t="str">
+        <v/>
+      </c>
+      <c r="N11" s="4" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5">
+      <c r="A12" s="4">
         <v>1234</v>
       </c>
-      <c r="B12" s="5" t="str">
+      <c r="B12" s="4" t="str">
         <v>CO</v>
       </c>
-      <c r="C12" s="5" t="str">
-        <v/>
-      </c>
-      <c r="D12" s="5" t="str">
+      <c r="C12" s="4" t="str">
+        <v/>
+      </c>
+      <c r="D12" s="4" t="str">
         <v>ZZ-23</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>8</v>
       </c>
-      <c r="F12" s="5" t="str">
-        <v/>
-      </c>
-      <c r="G12" s="5" t="str">
-        <v/>
-      </c>
-      <c r="H12" s="5" t="str">
-        <v/>
-      </c>
-      <c r="I12" s="5" t="str">
+      <c r="F12" s="4" t="str">
+        <v/>
+      </c>
+      <c r="G12" s="4" t="str">
+        <v/>
+      </c>
+      <c r="H12" s="4" t="str">
+        <v/>
+      </c>
+      <c r="I12" s="4" t="str">
         <v>Visit was delayed by a day due to hospital holiday</v>
       </c>
-      <c r="J12" s="5" t="str">
-        <v/>
-      </c>
-      <c r="K12" s="5" t="str">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="str">
+      <c r="J12" s="4" t="str">
+        <v/>
+      </c>
+      <c r="K12" s="4" t="str">
+        <v/>
+      </c>
+      <c r="L12" s="4" t="str">
         <v>PRINCIPAL INVESTIGATOR</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="4">
         <v>4</v>
       </c>
-      <c r="N12" s="5" t="str">
+      <c r="N12" s="4" t="str">
         <v/>
       </c>
     </row>
